--- a/Nutzwertanalyse_Glättung.xlsx
+++ b/Nutzwertanalyse_Glättung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a471988a8a86cc1/Studium/Bachelor/Artefakte/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="8_{07ADA279-FDEA-4443-8009-F886D968C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70EB8058-742D-4DE2-B679-4BA7BC8DFCD4}"/>
+  <xr:revisionPtr revIDLastSave="309" documentId="8_{07ADA279-FDEA-4443-8009-F886D968C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{313D2B3E-86AA-4B03-9D1B-5F72EA94EC6A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{20C679E4-C9D8-48C4-B659-4235CD5DE514}"/>
+    <workbookView xWindow="-28920" yWindow="345" windowWidth="29040" windowHeight="15720" xr2:uid="{20C679E4-C9D8-48C4-B659-4235CD5DE514}"/>
   </bookViews>
   <sheets>
     <sheet name="Szenarien" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Szenario 3" sheetId="11" r:id="rId6"/>
     <sheet name="Szenario 4" sheetId="12" r:id="rId7"/>
     <sheet name="Szenario 5" sheetId="13" r:id="rId8"/>
-    <sheet name="Szenario 0 - Referenz" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="39">
   <si>
     <t>Szenario</t>
   </si>
@@ -259,12 +258,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
@@ -276,6 +269,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -370,9 +369,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -381,56 +380,56 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,84 +780,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="E1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15">
         <v>32.5</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>5</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="15">
         <v>32.5</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="10">
         <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="7">
         <v>5</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="15">
-        <v>10</v>
-      </c>
-      <c r="K2" s="12">
-        <v>5</v>
-      </c>
-      <c r="L2" s="4">
+      <c r="J2" s="10">
+        <v>10</v>
+      </c>
+      <c r="K2" s="7">
+        <v>5</v>
+      </c>
+      <c r="L2" s="21">
         <f t="shared" ref="L2:L7" si="0">SUM(B2:K2)</f>
         <v>100</v>
       </c>
@@ -866,241 +865,241 @@
         <f>AVERAGE(L2:L6)</f>
         <v>100</v>
       </c>
-      <c r="N2" s="16"/>
+      <c r="N2" s="11"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13">
-        <v>15</v>
-      </c>
-      <c r="C3" s="15">
-        <v>10</v>
-      </c>
-      <c r="D3" s="13">
-        <v>15</v>
-      </c>
-      <c r="E3" s="12">
-        <v>5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>15</v>
-      </c>
-      <c r="G3" s="13">
-        <v>15</v>
-      </c>
-      <c r="H3" s="12">
+      <c r="A3" s="20">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10">
+        <v>10</v>
+      </c>
+      <c r="D3" s="8">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+      <c r="F3" s="8">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8">
+        <v>15</v>
+      </c>
+      <c r="H3" s="7">
         <v>5</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
-      <c r="J3" s="13">
-        <v>15</v>
-      </c>
-      <c r="K3" s="12">
-        <v>5</v>
-      </c>
-      <c r="L3" s="4">
+      <c r="J3" s="8">
+        <v>15</v>
+      </c>
+      <c r="K3" s="7">
+        <v>5</v>
+      </c>
+      <c r="L3" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="M3" s="24"/>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="20">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8">
         <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>10</v>
       </c>
-      <c r="D4" s="13">
-        <v>15</v>
-      </c>
-      <c r="E4" s="12">
-        <v>5</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="D4" s="8">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7">
         <v>5</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="H4" s="13">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13">
-        <v>15</v>
-      </c>
-      <c r="J4" s="13">
-        <v>15</v>
-      </c>
-      <c r="K4" s="12">
-        <v>5</v>
-      </c>
-      <c r="L4" s="4">
+      <c r="H4" s="8">
+        <v>15</v>
+      </c>
+      <c r="I4" s="8">
+        <v>15</v>
+      </c>
+      <c r="J4" s="8">
+        <v>15</v>
+      </c>
+      <c r="K4" s="7">
+        <v>5</v>
+      </c>
+      <c r="L4" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="M4" s="24"/>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15">
-        <v>10</v>
-      </c>
-      <c r="D5" s="15">
-        <v>10</v>
-      </c>
-      <c r="E5" s="15">
-        <v>10</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="B5" s="10">
+        <v>10</v>
+      </c>
+      <c r="C5" s="10">
+        <v>10</v>
+      </c>
+      <c r="D5" s="10">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10">
+        <v>10</v>
+      </c>
+      <c r="F5" s="8">
         <v>15</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
-        <v>15</v>
-      </c>
-      <c r="I5" s="13">
-        <v>15</v>
-      </c>
-      <c r="J5" s="15">
-        <v>10</v>
-      </c>
-      <c r="K5" s="12">
-        <v>5</v>
-      </c>
-      <c r="L5" s="4">
+      <c r="H5" s="8">
+        <v>15</v>
+      </c>
+      <c r="I5" s="8">
+        <v>15</v>
+      </c>
+      <c r="J5" s="10">
+        <v>10</v>
+      </c>
+      <c r="K5" s="7">
+        <v>5</v>
+      </c>
+      <c r="L5" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18">
-        <v>5</v>
-      </c>
-      <c r="C6" s="17">
-        <v>15</v>
-      </c>
-      <c r="D6" s="19">
-        <v>10</v>
-      </c>
-      <c r="E6" s="19">
-        <v>10</v>
-      </c>
-      <c r="F6" s="17">
-        <v>15</v>
-      </c>
-      <c r="G6" s="17">
-        <v>15</v>
-      </c>
-      <c r="H6" s="19">
-        <v>10</v>
-      </c>
-      <c r="I6" s="18">
-        <v>5</v>
-      </c>
-      <c r="J6" s="18">
-        <v>5</v>
-      </c>
-      <c r="K6" s="19">
-        <v>10</v>
-      </c>
-      <c r="L6" s="4">
+      <c r="A6" s="22">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12">
+        <v>15</v>
+      </c>
+      <c r="D6" s="14">
+        <v>10</v>
+      </c>
+      <c r="E6" s="14">
+        <v>10</v>
+      </c>
+      <c r="F6" s="12">
+        <v>15</v>
+      </c>
+      <c r="G6" s="12">
+        <v>15</v>
+      </c>
+      <c r="H6" s="14">
+        <v>10</v>
+      </c>
+      <c r="I6" s="13">
+        <v>5</v>
+      </c>
+      <c r="J6" s="13">
+        <v>5</v>
+      </c>
+      <c r="K6" s="14">
+        <v>10</v>
+      </c>
+      <c r="L6" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="20">
         <v>0</v>
       </c>
-      <c r="B7" s="9">
-        <v>10</v>
-      </c>
-      <c r="C7" s="9">
-        <v>10</v>
-      </c>
-      <c r="D7" s="9">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9">
-        <v>10</v>
-      </c>
-      <c r="G7" s="9">
-        <v>10</v>
-      </c>
-      <c r="H7" s="9">
-        <v>10</v>
-      </c>
-      <c r="I7" s="9">
-        <v>10</v>
-      </c>
-      <c r="J7" s="9">
-        <v>10</v>
-      </c>
-      <c r="K7" s="9">
-        <v>10</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="B7" s="4">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4">
+        <v>10</v>
+      </c>
+      <c r="J7" s="4">
+        <v>10</v>
+      </c>
+      <c r="K7" s="4">
+        <v>10</v>
+      </c>
+      <c r="L7" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="M7" s="25"/>
-      <c r="N7" s="16"/>
+      <c r="N7" s="11"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="D10" s="21" t="s">
+      <c r="B10" s="9"/>
+      <c r="D10" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="10"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1161,16 +1160,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1315,18 +1314,18 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="19">
         <f>SUM(B2:B11)</f>
         <v>24</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="19">
         <f t="shared" ref="C12:D12" si="0">SUM(C2:C11)</f>
         <v>23</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="19">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1355,48 +1354,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1731,67 +1730,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="e">
+      <c r="B13" s="19" t="e">
         <f>SUM(B3:B12)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="e">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="e">
         <f t="shared" ref="D13:H13" si="3">SUM(D3:D12)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="e">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="e">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6" t="e">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19" t="e">
         <f>(D13-100)/2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6" t="e">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19" t="e">
         <f>(F13-100)/2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="e">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19" t="e">
         <f>(H13-100)/2</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6" t="e">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="e">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="e">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19" t="e">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6" t="e">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19" t="e">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>#VALUE!</v>
       </c>
@@ -1829,48 +1828,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="17">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2205,67 +2204,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="19">
         <f>SUM(B3:B12)</f>
         <v>100</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
         <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
         <v>230</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
         <f t="shared" si="6"/>
         <v>227.5</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <f t="shared" si="6"/>
         <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19">
         <f>(D13-100)/2</f>
         <v>65</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
         <f>(F13-100)/2</f>
         <v>63.75</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <f>(H13-100)/2</f>
         <v>77.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>3</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>1</v>
       </c>
@@ -2303,48 +2302,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5">
-        <v>2</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="17">
+        <v>2</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2679,67 +2678,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="19">
         <f>SUM(B3:B12)</f>
         <v>100</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
         <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
         <v>235</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
         <f t="shared" si="6"/>
         <v>215</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <f t="shared" si="6"/>
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19">
         <f>(D13-100)/2</f>
         <v>67.5</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
         <f>(F13-100)/2</f>
         <v>57.5</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <f>(H13-100)/2</f>
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>2</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>3</v>
       </c>
@@ -2777,48 +2776,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5">
-        <v>3</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="17">
+        <v>3</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3153,67 +3152,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="19">
         <f>SUM(B3:B12)</f>
         <v>100</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
         <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
         <v>210</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <f t="shared" si="6"/>
         <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19">
         <f>(D13-100)/2</f>
         <v>55</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
         <f>(F13-100)/2</f>
         <v>70</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <f>(H13-100)/2</f>
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>1</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>3</v>
       </c>
@@ -3251,48 +3250,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5">
+      <c r="B1" s="17">
         <v>4</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3627,67 +3626,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="19">
         <f>SUM(B3:B12)</f>
         <v>100</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
         <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
         <v>230</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
         <f t="shared" si="6"/>
         <v>245</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <f t="shared" si="6"/>
         <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19">
         <f>(D13-100)/2</f>
         <v>65</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
         <f>(F13-100)/2</f>
         <v>72.5</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <f>(H13-100)/2</f>
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>1</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>3</v>
       </c>
@@ -3725,48 +3724,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5">
-        <v>5</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="17">
+        <v>5</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4101,67 +4100,67 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="19">
         <f>SUM(B3:B12)</f>
         <v>100</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
         <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
         <v>255</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
         <f t="shared" si="6"/>
         <v>235</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <f t="shared" si="6"/>
         <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19">
         <f>(D13-100)/2</f>
         <v>77.5</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
         <f>(F13-100)/2</f>
         <v>67.5</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <f>(H13-100)/2</f>
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
         <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
         <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
         <v>2</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19">
         <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
         <v>3</v>
       </c>
@@ -4184,478 +4183,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EF8FD4-0E48-4BC3-A71A-44B08418BCE9}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="5">
-        <v>6</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="22"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" cm="1">
-        <f t="array" ref="B3">INDEX(Szenarien!B:K, $B$1+1, 1)</f>
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <f>Lösungen!B2</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <f>PRODUCT(B3,C3)</f>
-        <v>10</v>
-      </c>
-      <c r="E3" s="3">
-        <f>Lösungen!C2</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <f>PRODUCT(B3,E3)</f>
-        <v>20</v>
-      </c>
-      <c r="G3" s="3">
-        <f>Lösungen!D2</f>
-        <v>3</v>
-      </c>
-      <c r="H3" s="3">
-        <f>PRODUCT(B3,G3)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" cm="1">
-        <f t="array" ref="B4">INDEX(Szenarien!B:K, $B$1+1, 2)</f>
-        <v>10</v>
-      </c>
-      <c r="C4" s="3">
-        <f>Lösungen!B3</f>
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <f>PRODUCT(B4,C4)</f>
-        <v>30</v>
-      </c>
-      <c r="E4" s="3">
-        <f>Lösungen!C3</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="3">
-        <f>PRODUCT(B4,E4)</f>
-        <v>30</v>
-      </c>
-      <c r="G4" s="3">
-        <f>Lösungen!D3</f>
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <f>PRODUCT(B4,G4)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" cm="1">
-        <f t="array" ref="B5">INDEX(Szenarien!B:K, $B$1+1, 3)</f>
-        <v>10</v>
-      </c>
-      <c r="C5" s="3">
-        <f>Lösungen!B4</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <f t="shared" ref="D5:D9" si="0">PRODUCT(B5,C5)</f>
-        <v>10</v>
-      </c>
-      <c r="E5" s="3">
-        <f>Lösungen!C4</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="3">
-        <f t="shared" ref="F5:F9" si="1">PRODUCT(B5,E5)</f>
-        <v>30</v>
-      </c>
-      <c r="G5" s="3">
-        <f>Lösungen!D4</f>
-        <v>2</v>
-      </c>
-      <c r="H5" s="3">
-        <f t="shared" ref="H5:H9" si="2">PRODUCT(B5,G5)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" cm="1">
-        <f t="array" ref="B6">INDEX(Szenarien!B:K, $B$1+1, 4)</f>
-        <v>10</v>
-      </c>
-      <c r="C6" s="3">
-        <f>Lösungen!B5</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="3">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E6" s="3">
-        <f>Lösungen!C5</f>
-        <v>3</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G6" s="3">
-        <f>Lösungen!D5</f>
-        <v>3</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" cm="1">
-        <f t="array" ref="B7">INDEX(Szenarien!B:K, $B$1+1, 5)</f>
-        <v>10</v>
-      </c>
-      <c r="C7" s="3">
-        <f>Lösungen!B6</f>
-        <v>3</v>
-      </c>
-      <c r="D7" s="3">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E7" s="3">
-        <f>Lösungen!C6</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G7" s="3">
-        <f>Lösungen!D6</f>
-        <v>2</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" cm="1">
-        <f t="array" ref="B8">INDEX(Szenarien!B:K, $B$1+1, 6)</f>
-        <v>10</v>
-      </c>
-      <c r="C8" s="3">
-        <f>Lösungen!B7</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="3">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E8" s="3">
-        <f>Lösungen!C7</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="G8" s="3">
-        <f>Lösungen!D7</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" cm="1">
-        <f t="array" ref="B9">INDEX(Szenarien!B:K, $B$1+1, 7)</f>
-        <v>10</v>
-      </c>
-      <c r="C9" s="3">
-        <f>Lösungen!B8</f>
-        <v>2</v>
-      </c>
-      <c r="D9" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E9" s="3">
-        <f>Lösungen!C8</f>
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G9" s="3">
-        <f>Lösungen!D8</f>
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" cm="1">
-        <f t="array" ref="B10">INDEX(Szenarien!B:K, $B$1+1, 8)</f>
-        <v>10</v>
-      </c>
-      <c r="C10" s="3">
-        <f>Lösungen!B9</f>
-        <v>2</v>
-      </c>
-      <c r="D10" s="3">
-        <f>PRODUCT(B10,C10)</f>
-        <v>20</v>
-      </c>
-      <c r="E10" s="3">
-        <f>Lösungen!C9</f>
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
-        <f>PRODUCT(B10,E10)</f>
-        <v>30</v>
-      </c>
-      <c r="G10" s="3">
-        <f>Lösungen!D9</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <f>PRODUCT(B10,G10)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" cm="1">
-        <f t="array" ref="B11">INDEX(Szenarien!B:K, $B$1+1, 9)</f>
-        <v>10</v>
-      </c>
-      <c r="C11" s="3">
-        <f>Lösungen!B10</f>
-        <v>3</v>
-      </c>
-      <c r="D11" s="3">
-        <f>PRODUCT(B11,C11)</f>
-        <v>30</v>
-      </c>
-      <c r="E11" s="3">
-        <f>Lösungen!C10</f>
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <f>PRODUCT(B11,E11)</f>
-        <v>10</v>
-      </c>
-      <c r="G11" s="3">
-        <f>Lösungen!D10</f>
-        <v>2</v>
-      </c>
-      <c r="H11" s="3">
-        <f>PRODUCT(B11,G11)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" cm="1">
-        <f t="array" ref="B12">INDEX(Szenarien!B:K, $B$1+1, 10)</f>
-        <v>10</v>
-      </c>
-      <c r="C12" s="3">
-        <f>Lösungen!B11</f>
-        <v>3</v>
-      </c>
-      <c r="D12" s="3">
-        <f t="shared" ref="D12" si="3">PRODUCT(B12,C12)</f>
-        <v>30</v>
-      </c>
-      <c r="E12" s="3">
-        <f>Lösungen!C11</f>
-        <v>1</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" ref="F12" si="4">PRODUCT(B12,E12)</f>
-        <v>10</v>
-      </c>
-      <c r="G12" s="3">
-        <f>Lösungen!D11</f>
-        <v>2</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" ref="H12" si="5">PRODUCT(B12,G12)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="6">
-        <f>SUM(B3:B12)</f>
-        <v>100</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
-        <f t="shared" ref="D13:H13" si="6">SUM(D3:D12)</f>
-        <v>240</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
-        <f t="shared" si="6"/>
-        <v>230</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
-        <f t="shared" si="6"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
-        <f>(D13-100)/2</f>
-        <v>70</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
-        <f>(F13-100)/2</f>
-        <v>65</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
-        <f>(H13-100)/2</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6">
-        <f>1+(F13&gt;D13)+(H13&gt;D13)</f>
-        <v>1</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
-        <f>1+(D13&gt;F13)+(H13&gt;F13)</f>
-        <v>2</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
-        <f>1+(D13&gt;H13)+(F13&gt;H13)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>